--- a/samples/ss_pmlng_ingest.xlsx
+++ b/samples/ss_pmlng_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,27 +758,21 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -822,35 +801,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -879,35 +849,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -936,35 +897,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -993,23 +945,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>30/60/60 MVA + 25 MVAR</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1025,7 +970,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1054,23 +998,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>3x60 MVA + 25 MVAR</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1086,7 +1023,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1115,35 +1051,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1172,23 +1099,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>3x60 MVA + 25 MVAR (kapasitor 1 PMS busbar)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1204,7 +1124,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1233,35 +1152,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1290,17 +1200,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>batas ke Subsistem Mandirancan (UP2B Jabar)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1326,7 +1230,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1433,7 +1336,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT New Batang - Bumi Putih</t>
@@ -1454,7 +1356,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -1468,8 +1369,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1486,13 +1385,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT New Batang - Weleri Bus 1</t>
@@ -1513,7 +1410,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -1527,8 +1423,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1545,13 +1439,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Bumi Putih - Weleri</t>
@@ -1572,7 +1464,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -1586,8 +1477,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1604,13 +1493,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTT New Batang - Batang</t>
@@ -1631,7 +1518,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -1645,8 +1531,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1663,7 +1547,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1694,7 +1577,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1708,8 +1590,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1726,13 +1606,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Pekalongan - Comal</t>
@@ -1753,7 +1631,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1767,8 +1644,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1785,13 +1660,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Comal - Pemalang</t>
@@ -1812,7 +1685,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1826,8 +1698,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1844,13 +1714,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Pemalang - Tarub</t>
@@ -1871,7 +1739,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1885,8 +1752,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1903,7 +1768,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1934,7 +1798,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1948,8 +1811,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1966,7 +1827,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2045,12 +1905,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Rekonfigurasi jaringan di GI Kebasen ke Subsistem Mandirancan. 2.Sudah terpasang OLS IBT Pemalang 1,2sebesar451MW (Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 3.Pengaturan pemeliharaan saat beban rendah/hari libur</t>
+          <t>1. Rekonfigurasi jaringan di GI Kebasen ke Subsistem Mandirancan. 2. Sudah terpasang OLS IBT Pemalang 1,2 sebesar451MW (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 3. Pengaturan pemeliharaan saat beban rendah/hari libur</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan extension IBT ke-3&amp;4 Pemalang/New Batang beserta SUTT 150 kV New Batang-Comal dan SUTT 150 kV New Batang-KIT Batang.SesuaiRUPTL 2025- 2034, COD 2027). 2.Pembangunan SUTT 150 kV Dieng -New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027</t>
+          <t>Jangka Pendek : 1. Pembangunan extension IBT ke-3&amp;4 Pemalang/New Batang beserta SUTT 150 kV New Batang-Comal dan SUTT 150 kV New Batang-KIT Batang. SesuaiRUPTL 2025- 2034, COD 2027). 2. Pembangunan SUTT 150 kV Dieng - New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -2080,12 +1940,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Rekonfigurasi jaringan di GI Kebasen ke Subsistem Mandirancan. 2.Sudah terpasang OLS SUTT 150 kV Batang- Pekalongan 1,2sebesar376MW (Realisasi BP Tahun 2025, 14 Oktober 2025-5721MW)</t>
+          <t>1. Rekonfigurasi jaringan di GI Kebasen ke Subsistem Mandirancan. 2. Sudah terpasang OLS SUTT 150 kV Batang - Pekalongan 1,2 sebesar376MW (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721MW)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan extension IBT ke-3&amp;4 Pemalang/Batang beserta SUTT 150 kV New Batang-ComaldanSUTT 150 kV New Batang-KIT Batang terkait,sesuaiRUPTL 2025- 2034, COD 2027). Line Bay masuk di section IBT 3,4Pemalang/Batang</t>
+          <t>Jangka Pendek : Pembangunan extension IBT ke-3&amp;4 Pemalang/Batang beserta SUTT 150 kV New Batang-Comal dan SUTT 150 kV New Batang-KIT Batang terkait, sesuaiRUPTL 2025- 2034, COD 2027). Line Bay masuk di section IBT 3,4 Pemalang/Batang</t>
         </is>
       </c>
     </row>
@@ -2115,12 +1975,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Pekerjaan dilakukan secara PDKB. 2.Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Pekerjaan dilakukan secara PDKB. 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>JangkaPendek: Usulan baru pembangunan PMS busbar ke-2 GI 150 kV Pemalang. diusulkanCODTahun 2026. Kajian telah dikirim TW4 2025</t>
+          <t>Jangka Pendek: Usulan baru pembangunan PMS busbar ke-2 GI 150 kV Pemalang. diusulkan CODTahun 2026. Kajian telah dikirim TW4 2025</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2000,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Tegangan rendah pada wilayah Tegal yaitu pada GI 150 kV Kebasen dan GI 150 kV Brebes saat periode outage PLTU CEP. Serta adanya rencana pembangunan GI Brebes II yang berpotensimenambah pembebanan dan menurunkan kualitas tegangan di GI Brebes</t>
+          <t>[BELUM_DITETAPKAN] Tegangan rendah pada wilayah Tegal yaitu pada GI 150 kV Kebasen dan GI 150 kV Brebes saat periode outage PLTU CEP. Serta adanya rencana pembangunan GI Brebes II yang berpotensi menambah pembebanan dan menurunkan kualitas tegangan di GI Brebes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2150,12 +2010,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Rekonfigurasi pada Subsistem Pemalang 1,2 dan Subsistem Kesugihan 1,2 pada GI Kebasen dengan operasi split bus pada GI Kebasen. 2.Mengoperasikan kapasitor kebasen 25 MVAR secara terus menerus</t>
+          <t>1. Rekonfigurasi pada Subsistem Pemalang 1,2 dan Subsistem Kesugihan 1,2 pada GI Kebasen dengan operasi split bus pada GI Kebasen. 2. Mengoperasikan kapasitor kebasen 25 MVAR secara terus menerus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Usulan baru uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027. Progres: 0%. Prioritas: P2. (Usulan AI Tahun 2026 UIT JBT). 2.Usulan pemasangan kapasitordi GI Brebes sebesar 50 MVAR. Rencana COD tahun 2026/2027 Usulan / Solusi Progres: 0%. Prioritas: P1 (tobe confirm)</t>
+          <t>Jangka Pendek : 1. Usulan baru uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027. Progres: 0%. Prioritas: P2. (Usulan AI Tahun 2026 UIT JBT). 2. Usulan pemasangan kapasitor di GI Brebes sebesar 50 MVAR. Rencana COD tahun 2026/2027 Usulan / Solusi Progres: 0%. Prioritas: P1 (tobe confirm)</t>
         </is>
       </c>
     </row>
